--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>29/08 18:20</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>225</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>28/08 18:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>225</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>29/08 15:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>225.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>225</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>29/08 17:00</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>28/08 17:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>175</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>28/08 18:15</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>175</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>28/08 18:20</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>175</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>28/08 17:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>175</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>29/08 15:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>150</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>25/08 16:10</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>140</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>28/08 17:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>140</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>29/08 17:45</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>125</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>29/08 17:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>125.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>125</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>27/08 00:10</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>100</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>25/08 13:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>60</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>31/08 00:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>60</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>26/08 00:10</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>70</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>25/08 17:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>55</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>25/08 20:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>55</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>26/08 16:10</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>60</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>27/08 00:10</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>60</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>31/08 23:20</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>60</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>31/08 14:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>50</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>25/08 22:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>50</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>31/08 16:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>9</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,142 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45894.07554379525</v>
+        <v>45894.07554379629</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 1 (−2.5) | Christophe</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Christopher O'Connell – Alex De MinaurUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>H 1 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>26/08 20:10</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+21,6%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45894.13685908308</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | RB Salzbou</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>RB Salzbourg – Blau-Weiss LinzBundesliga</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>30/08 15:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+21,4%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45894.13685908308</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Aarhus GF </t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Aarhus GF – FC FredericiaSuperLiga</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>31/08 12:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+20,5%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45894.13685908308</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>26/08 20:10</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>60</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45894.13685908308</v>
+        <v>45894.13685908565</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>30/08 15:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>55</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45894.13685908308</v>
+        <v>45894.13685908565</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>31/08 12:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>55</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,52 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45894.13685908308</v>
+        <v>45894.13685908565</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Club Olimp</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Club Olimpia – Club Sportivo LuquenoPrimera Division</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>30/08 21:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2,50%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+50,2%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45894.1874137616</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>30/08 21:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>60</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,52 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45894.1874137616</v>
+        <v>45894.18741376157</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis | Plus que 1.5 - tie-break | Opelka, Re</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Opelka, Reilly – Alcaraz, CarlosEvénements. US Open (H)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 1.5 - tie-break</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>26/08 01:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>24,9%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+37,2%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45894.22493348684</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>26/08 01:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="F31" t="n">
+        <v>5.5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,97 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45894.22493348684</v>
+        <v>45894.2249334838</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey | Pas de buts | Kometa Brn</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Kometa Brno – Brynäs IFInternational - ChampionsLeague</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>29/08 17:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>100.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+89,4%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45894.27433432001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 16.5 - tirs1re équipe | Club Bruge</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Club Bruges – Glasgow RangersEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 16.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>27/08 19:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>42,1%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+26,2%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45894.27433432001</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>29/08 17:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>100.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>100</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45894.27433432001</v>
+        <v>45894.27433431713</v>
       </c>
     </row>
     <row r="33">
@@ -1840,10 +1838,8 @@
           <t>27/08 19:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>3</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1856,7 +1852,142 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45894.27433432001</v>
+        <v>45894.27433431713</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Storhamar </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Storhamar IL Dragons – Eisbären BerlinEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>28/08 17:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+162%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45894.30697939201</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Kometa Brn</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Kometa Brno – Brynäs IFEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>29/08 17:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+160%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45894.30697939201</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lulea HF –</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Lulea HF – EV ZugLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>28/08 17:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+151%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45894.30697939201</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1881,10 +1881,8 @@
           <t>28/08 17:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>175</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45894.30697939201</v>
+        <v>45894.30697938657</v>
       </c>
     </row>
     <row r="35">
@@ -1926,10 +1924,8 @@
           <t>29/08 17:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>140</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1942,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45894.30697939201</v>
+        <v>45894.30697938657</v>
       </c>
     </row>
     <row r="36">
@@ -1971,10 +1967,8 @@
           <t>28/08 17:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>150</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1987,7 +1981,97 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45894.30697939201</v>
+        <v>45894.30697938657</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Frolunda –</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Frolunda – HC Bolzano-Bozen FoxesLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>29/08 17:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,60%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+180%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45894.3552397673</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | San Lorenz</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>San Lorenzo – CA HuracanLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>30/08 17:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>75.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+32,6%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45894.3552397673</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,10 +2010,8 @@
           <t>29/08 17:00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>175</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2026,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45894.3552397673</v>
+        <v>45894.35523976852</v>
       </c>
     </row>
     <row r="38">
@@ -2055,10 +2053,8 @@
           <t>30/08 17:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>75.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>75</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2071,7 +2067,142 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45894.3552397673</v>
+        <v>45894.35523976852</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lukko – La</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Lukko – LausanneEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>29/08 15:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+177%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45894.39254436806</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Maccabi Te</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Maccabi Tel Aviv – Maccabi NetanyaPremier League</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>31/08 17:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+53,8%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45894.39254436806</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Grenade – </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Grenade – MirandesLaLiga2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>31/08 19:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+16,7%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45894.39254436806</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>29/08 15:30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>175</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45894.39254436806</v>
+        <v>45894.39254436343</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>31/08 17:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>65</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45894.39254436806</v>
+        <v>45894.39254436343</v>
       </c>
     </row>
     <row r="41">
@@ -2186,10 +2182,8 @@
           <t>31/08 19:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>55</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2202,7 +2196,52 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45894.39254436806</v>
+        <v>45894.39254436343</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball | H 1 (−40.5)P | Serbie – E</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Serbie – EstonieEurope - EuroBasket</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>H 1 (−40.5)P</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>27/08 18:15</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>23,9%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+26,7%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45894.43388981897</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2225,10 +2225,8 @@
           <t>27/08 18:15</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>5.30</t>
-        </is>
+      <c r="F42" t="n">
+        <v>5.3</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,97 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45894.43388981897</v>
+        <v>45894.43388981481</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Genclerbir</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Genclerbirligi – FenerbahceSüper Lig</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>31/08 16:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2,10%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+26,2%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45894.47166802892</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 2 (−2.5) | Novak Djok</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Novak Djokovic – Zachary SvajdaUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>H 2 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>27/08 15:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+15,9%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45894.47166802892</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2268,10 +2268,8 @@
           <t>31/08 16:00</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>60</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45894.47166802892</v>
+        <v>45894.47166803241</v>
       </c>
     </row>
     <row r="44">
@@ -2313,10 +2311,8 @@
           <t>27/08 15:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>50</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2329,7 +2325,97 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45894.47166802892</v>
+        <v>45894.47166803241</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Ingolstadt</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ingolstadt – Ilves TampereEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>28/08 17:30</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+169%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45894.53167342866</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Racing San</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Racing Santander – Ad CeutaLaLiga2</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>30/08 15:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+36,1%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45894.53167342866</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,10 +2354,8 @@
           <t>28/08 17:30</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>175</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45894.53167342866</v>
+        <v>45894.53167342592</v>
       </c>
     </row>
     <row r="46">
@@ -2399,10 +2397,8 @@
           <t>30/08 15:00</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>60</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2415,7 +2411,97 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45894.53167342866</v>
+        <v>45894.53167342592</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | H 1 (−2.5) | Hugo Delli</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Hugo Dellien – Kamil MajchrzakUS Open (H)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>H 1 (−2.5)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>25/08 18:10</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+36,1%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45894.56454850013</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | River Plat</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>River Plate – San Martin de San JuanLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>31/08 22:15</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+11,6%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45894.56454850013</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -2440,10 +2440,8 @@
           <t>25/08 18:10</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>65</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45894.56454850013</v>
+        <v>45894.56454849537</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>31/08 22:15</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F48" t="n">
+        <v>50</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45894.56454850013</v>
+        <v>45894.56454849537</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2500,6 +2500,96 @@
         <v>45894.56454849537</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Burnley – </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Burnley – Derby CountyEFL Cup</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>26/08 18:45</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+13,1%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45894.64145961245</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis | Plus que 1.5 - tie-break | Shelton, B</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PMU(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Shelton, Ben – Carreno Busta, PabloEvénements. US Open (H)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 1.5 - tie-break</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>26/08 14:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>17,0%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+10,7%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45894.64145961245</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -2526,10 +2526,8 @@
           <t>26/08 18:45</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F49" t="n">
+        <v>55</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2542,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45894.64145961245</v>
+        <v>45894.64145961805</v>
       </c>
     </row>
     <row r="50">
@@ -2571,10 +2569,8 @@
           <t>26/08 14:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="F50" t="n">
+        <v>6.5</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2587,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45894.64145961245</v>
+        <v>45894.64145961805</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2586,6 +2586,51 @@
         <v>45894.64145961805</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | RB Salzbou</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>RB Salzbourg – Gorniczy Klub Sportowy TychyLigue des Champions</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>29/08 18:20</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+223%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45894.72087349922</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,10 +2612,8 @@
           <t>29/08 18:20</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F51" t="n">
+        <v>200</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2628,7 +2626,97 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>45894.72087349922</v>
+        <v>45894.72087349537</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Racing Clu</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Racing Club – Union Santa FeLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>01/09 00:15</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+28,4%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45894.7721368608</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | FC Ashdod </t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>FC Ashdod – Bnei Sakhnin FCPremier League</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>30/08 17:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+14,7%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45894.7721368608</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -2655,10 +2655,8 @@
           <t>01/09 00:15</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F52" t="n">
+        <v>60</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45894.7721368608</v>
+        <v>45894.77213686342</v>
       </c>
     </row>
     <row r="53">
@@ -2700,10 +2698,8 @@
           <t>30/08 17:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F53" t="n">
+        <v>45</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2716,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45894.7721368608</v>
+        <v>45894.77213686342</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2715,6 +2715,51 @@
         <v>45894.77213686342</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Real Socie</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Real Sociedad B – AlmeriaLaLiga2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>29/08 17:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+14,1%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45894.84983606439</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2741,10 +2741,8 @@
           <t>29/08 17:30</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>50</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2757,7 +2755,52 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45894.84983606439</v>
+        <v>45894.84983606482</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Internacio</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Internacional – FortalezaSérie A</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>31/08 23:30</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+20,7%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45894.88896995848</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2784,23 +2784,156 @@
           <t>31/08 23:30</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" t="n">
+        <v>60</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+20,7%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45894.8889699537</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | TSC Backa </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>TSC Backa Topola – Javor IvanjicaSuperLiga</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>30/08 17:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>60.00</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>+20,7%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>45894.88896995848</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+39,6%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45894.93116416513</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Cadix – Al</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Cadix – AlbaceteLaLiga2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>31/08 15:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+17,4%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45894.93116416513</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Sturm Graz</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Sturm Graz – Bodø/GlimtEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>26/08 19:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>45,6%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+14,0%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45894.93116416513</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-25.xlsx
+++ b/data/valuebets_database_2025-08-25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>30/08 17:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F56" t="n">
+        <v>60</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45894.93116416513</v>
+        <v>45894.93116416666</v>
       </c>
     </row>
     <row r="57">
@@ -2872,10 +2870,8 @@
           <t>31/08 15:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>55</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2888,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45894.93116416513</v>
+        <v>45894.93116416666</v>
       </c>
     </row>
     <row r="58">
@@ -2917,10 +2913,8 @@
           <t>26/08 19:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F58" t="n">
+        <v>2.5</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2933,7 +2927,97 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45894.93116416513</v>
+        <v>45894.93116416666</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | CA Aldosiv</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CA Aldosivi – Boca JuniorsLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>31/08 17:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+25,6%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45894.97248140907</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Galatasara</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Galatasaray – Caykur RizesporSüper Lig</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>30/08 18:30</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,10%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+15,3%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45894.97248140907</v>
       </c>
     </row>
   </sheetData>
